--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/计划表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/计划表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,6 +646,135 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>V1.8_20260613173932_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>L1机房准备</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>已派发</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>90</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>机房改造实施</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>已派发</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>90</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>工程勘测</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>100</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>V2.2_20260614213043_DRB</t>
         </is>
       </c>
     </row>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/计划表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/计划表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,135 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L1机房准备</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>已派发</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>90</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>机房改造实施</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>已派发</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>90</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>工程勘测</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>100</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>V2.3_20260614220356_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/计划表.xlsx
+++ b/data/projects/70e5ca737ae5433e9f0f3134d216acf7/早期介入/交付预案/输出结果/计划表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,135 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>L1机房准备</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>已派发</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>90</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>机房改造实施</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>已派发</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>90</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>工程勘测</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-08-16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-09-20</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>王长龙</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>V2.4_20260615171738_DRB</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
